--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,698 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127925431</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hopsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>515937</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6691727</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosöksspår på gran.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127925434</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hopsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>515939</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6691729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127925438</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hopsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>515986</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6691778</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127918037</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105494</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramptjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515951</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6691703</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127925424</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79052</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hopsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>515932</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691725</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127925426</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79052</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>185</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hopsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>515940</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6691728</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127925431</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127925434</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127925424</v>
       </c>
       <c r="B7" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127925426</v>
       </c>
       <c r="B8" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127925431</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127925434</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127925424</v>
       </c>
       <c r="B7" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127925426</v>
       </c>
       <c r="B8" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127925431</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127925434</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127925424</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127925426</v>
       </c>
       <c r="B8" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127925431</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127925434</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127925424</v>
       </c>
       <c r="B7" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127925426</v>
       </c>
       <c r="B8" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127925431</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127925434</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127925438</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>127918037</v>
       </c>
       <c r="B6" t="n">
-        <v>105609</v>
+        <v>105630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>127925424</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127925426</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112985163</v>
+        <v>127925424</v>
       </c>
       <c r="B2" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramptjärnen (Ramptjärnen), Dlr</t>
+          <t>Hopsveden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515976</v>
+        <v>515932</v>
       </c>
       <c r="R2" t="n">
-        <v>6691759</v>
+        <v>6691725</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127925431</v>
+        <v>127925426</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hopsveden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515937</v>
+        <v>515940</v>
       </c>
       <c r="R3" t="n">
-        <v>6691727</v>
+        <v>6691728</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosöksspår på gran.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127925434</v>
+        <v>127925431</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,20 +917,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -953,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515939</v>
+        <v>515937</v>
       </c>
       <c r="R4" t="n">
-        <v>6691729</v>
+        <v>6691727</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosöksspår på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,46 +1009,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127925438</v>
+        <v>127925434</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515986</v>
+        <v>515939</v>
       </c>
       <c r="R5" t="n">
-        <v>6691778</v>
+        <v>6691729</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1114,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,60 +1132,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127918037</v>
+        <v>112985242</v>
       </c>
       <c r="B6" t="n">
-        <v>105630</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramptjärnen, Dlr</t>
+          <t>Ramptjärnen, Ramptjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515951</v>
+        <v>516031</v>
       </c>
       <c r="R6" t="n">
-        <v>6691703</v>
+        <v>6691732</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,12 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,67 +1212,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127925424</v>
+        <v>112985163</v>
       </c>
       <c r="B7" t="n">
-        <v>79119</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hopsveden, Dlr</t>
+          <t>Ramptjärnen, Ramptjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515932</v>
+        <v>515975</v>
       </c>
       <c r="R7" t="n">
-        <v>6691725</v>
+        <v>6691759</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,57 +1320,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127925426</v>
+        <v>127925438</v>
       </c>
       <c r="B8" t="n">
-        <v>79119</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hopsveden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515940</v>
+        <v>515986</v>
       </c>
       <c r="R8" t="n">
-        <v>6691728</v>
+        <v>6691778</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1424,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,6 +1438,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1471,6 +1454,116 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127918037</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ramptjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>515951</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6691703</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37475-2025 artfynd.xlsx
+++ b/artfynd/A 37475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112985242</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127925424</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127925426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127925431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127925434</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112985163</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127925438</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,8 +1604,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127918037</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>